--- a/outputs/333-29.xlsx
+++ b/outputs/333-29.xlsx
@@ -227,75 +227,75 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/outputs/333-29.xlsx
+++ b/outputs/333-29.xlsx
@@ -831,7 +831,7 @@
       <c r="D4" s="17"/>
       <c r="E4" s="16"/>
       <c r="F4" s="18" t="n">
-        <v>41675</v>
+        <v>41673</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
